--- a/templates/data/revisoes_yamaha.xlsx
+++ b/templates/data/revisoes_yamaha.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\yamaha-bot\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\yamaha-bot\templates\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF159568-3AEA-4FF9-8AE9-7A7D3DD85E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3533B17A-12B5-4DF0-874D-B53E221F34FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CDFE129-51B5-418D-A7F1-200CBCD1D597}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="36">
   <si>
     <t>modelo</t>
   </si>
@@ -141,6 +141,17 @@
   </si>
   <si>
     <t>INJEÇÃO DE COMBUSTÍVEL|SISTEMA DE DIAGNÓTICO|BATERIA|FREIO DIANTEIRO|FREIO TRASEIRO|ROLAMENTOS DA DIREÇÃO|NTERRUPTOR DO CAVALETE LATERAL|ÓLEO DA TRANSMISSÃO FINAL|INTERRUPTORES DOS FREIOS DIANTEIRO E TRASEIRO|LUZES|PISCAS E INTERRUPTORES|FACHO DO FAROL|INJEÇÃO DE COMBUSTÍVEL MARCHA LENTA|MANGUEIRA VERIFICAÇÃO DO FILTRO DE AR|FILTRO DO ÓLEO DO MOTOR</t>
+  </si>
+  <si>
+    <t>YAMALUBE Scooter 10W40| ANEL DE BORRACHA da tampa de abastecimento de óleo do motor| CONTRAPINO| ANEL TRAVA||VELA DE IGNICAO (NGK CR6HSA)|GAXETA do dreno de óleo do motor|ANEL DE BORRACHA da tampa do filtro de óleo|VEDAÇÃO DO DUTO DE AR|GAXETA DA TAMPA DO CABECOTE|GAXETA DA TAMPA DA CARCACA 1</t>
+  </si>
+  <si>
+    <t>MANGUEIRA DE COMBUSTÍVEL/VELA DE IGNIÇÃO/INJEÇÃO DE COMBUSTÍVEL/SISTEMA DE ESCAPE/SISTEMA DE DIAGNÓSTICO/BATERIA/FREIO DIANTEIRO/FREIO TRASEIRO/MANGUEIRAS DO FREIO/RODAS/PNEUS/ROLAMENTOS DA RODA/ROLAMENTOS DA DIREÇÃO/FIXAÇÕES DO CHASSI/INTERRUPTOR DO CAVALETE LATERAL/GARFO DIANTEIRO/AMORTECEDOR TRASEIRO/CORREIA EM V/INTERRUPTORES DOS FREIOS DIANTEIRO E TRASEIRO/LUZES, PISCAS E INTERRUPTORES VÁLVULAS|FACHO DO FAROL AJUSTE
+VÁLVULAS/FACHO DO FAROL
+LIMPEZA
+MANGUEIRA VERIFICAÇÃO DO FILTRO DE AR/ELEMENTO DO FILTRO DE AR DA CAIXA DA CORREIA EM V/FILTRO DE ÓLEO DO MOTOR
+LUBRIFICAÇÃO
+EIXO ARTICULADO DO MANETE DE FREIO DIANTEIRO/EIXO ARTICULADO DO MANETE DE FREIO TRASEIRO/CAVALETE LATERAL/CAVALETE CENTRAL/CABOS E PEÇAS MOVÉIS/MANOPLA DO ACELERADOR</t>
   </si>
 </sst>
 </file>
@@ -199,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -214,6 +225,15 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -588,7 +608,9 @@
       <c r="D2" s="2">
         <v>6</v>
       </c>
-      <c r="E2" s="3"/>
+      <c r="E2" s="6">
+        <v>126</v>
+      </c>
       <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
@@ -618,7 +640,9 @@
       <c r="D3" s="2">
         <v>12</v>
       </c>
-      <c r="E3" s="3"/>
+      <c r="E3" s="6">
+        <v>126</v>
+      </c>
       <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
@@ -635,7 +659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -648,13 +672,19 @@
       <c r="D4" s="2">
         <v>18</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5">
+        <v>528</v>
+      </c>
       <c r="F4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5" t="s">
+      <c r="G4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>27</v>
       </c>
       <c r="J4" s="4" t="s">

--- a/templates/data/revisoes_yamaha.xlsx
+++ b/templates/data/revisoes_yamaha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\yamaha-bot\templates\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3533B17A-12B5-4DF0-874D-B53E221F34FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2073D8E-1F41-4674-A633-053B46716475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CDFE129-51B5-418D-A7F1-200CBCD1D597}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="36">
   <si>
     <t>modelo</t>
   </si>
@@ -857,7 +857,9 @@
         <v>18</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
+      <c r="F11" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
@@ -879,7 +881,9 @@
         <v>24</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
+      <c r="F12" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
@@ -901,7 +905,9 @@
         <v>30</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
+      <c r="F13" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
@@ -923,7 +929,9 @@
         <v>36</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
+      <c r="F14" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
@@ -945,7 +953,9 @@
         <v>42</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
+      <c r="F15" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
@@ -1015,7 +1025,9 @@
         <v>18</v>
       </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
+      <c r="F18" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
@@ -1037,7 +1049,9 @@
         <v>24</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+      <c r="F19" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
@@ -1059,7 +1073,9 @@
         <v>30</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
@@ -1081,7 +1097,9 @@
         <v>36</v>
       </c>
       <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
+      <c r="F21" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="5"/>
@@ -1103,7 +1121,9 @@
         <v>42</v>
       </c>
       <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
@@ -1173,7 +1193,9 @@
         <v>18</v>
       </c>
       <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
+      <c r="F25" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
@@ -1195,7 +1217,9 @@
         <v>24</v>
       </c>
       <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
@@ -1217,7 +1241,9 @@
         <v>30</v>
       </c>
       <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
+      <c r="F27" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -1239,7 +1265,9 @@
         <v>36</v>
       </c>
       <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -1261,7 +1289,9 @@
         <v>42</v>
       </c>
       <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
+      <c r="F29" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
@@ -1331,7 +1361,9 @@
         <v>18</v>
       </c>
       <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
+      <c r="F32" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
@@ -1353,7 +1385,9 @@
         <v>24</v>
       </c>
       <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
@@ -1375,7 +1409,9 @@
         <v>30</v>
       </c>
       <c r="E34" s="5"/>
-      <c r="F34" s="5"/>
+      <c r="F34" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
@@ -1397,7 +1433,9 @@
         <v>36</v>
       </c>
       <c r="E35" s="5"/>
-      <c r="F35" s="5"/>
+      <c r="F35" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
@@ -1419,7 +1457,9 @@
         <v>42</v>
       </c>
       <c r="E36" s="5"/>
-      <c r="F36" s="5"/>
+      <c r="F36" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="5"/>
@@ -1489,7 +1529,9 @@
         <v>18</v>
       </c>
       <c r="E39" s="5"/>
-      <c r="F39" s="5"/>
+      <c r="F39" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
@@ -1511,7 +1553,9 @@
         <v>24</v>
       </c>
       <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
+      <c r="F40" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
@@ -1533,7 +1577,9 @@
         <v>30</v>
       </c>
       <c r="E41" s="5"/>
-      <c r="F41" s="5"/>
+      <c r="F41" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="5"/>
@@ -1555,7 +1601,9 @@
         <v>36</v>
       </c>
       <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+      <c r="F42" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="5"/>
@@ -1577,7 +1625,9 @@
         <v>42</v>
       </c>
       <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+      <c r="F43" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="5"/>
@@ -1647,7 +1697,9 @@
         <v>18</v>
       </c>
       <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="F46" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
@@ -1669,7 +1721,9 @@
         <v>24</v>
       </c>
       <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="F47" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -1691,7 +1745,9 @@
         <v>30</v>
       </c>
       <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="F48" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -1713,7 +1769,9 @@
         <v>36</v>
       </c>
       <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="F49" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -1735,7 +1793,9 @@
         <v>42</v>
       </c>
       <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
+      <c r="F50" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -1805,7 +1865,9 @@
         <v>18</v>
       </c>
       <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="F53" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -1827,7 +1889,9 @@
         <v>24</v>
       </c>
       <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="F54" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -1849,7 +1913,9 @@
         <v>30</v>
       </c>
       <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
+      <c r="F55" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="5"/>
@@ -1871,7 +1937,9 @@
         <v>36</v>
       </c>
       <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
+      <c r="F56" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
@@ -1893,7 +1961,9 @@
         <v>42</v>
       </c>
       <c r="E57" s="5"/>
-      <c r="F57" s="5"/>
+      <c r="F57" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
@@ -1963,7 +2033,9 @@
         <v>18</v>
       </c>
       <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
+      <c r="F60" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
@@ -1985,7 +2057,9 @@
         <v>24</v>
       </c>
       <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="F61" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
@@ -2007,7 +2081,9 @@
         <v>30</v>
       </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="F62" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
@@ -2029,7 +2105,9 @@
         <v>36</v>
       </c>
       <c r="E63" s="5"/>
-      <c r="F63" s="5"/>
+      <c r="F63" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
@@ -2051,7 +2129,9 @@
         <v>42</v>
       </c>
       <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
+      <c r="F64" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
@@ -2121,7 +2201,9 @@
         <v>18</v>
       </c>
       <c r="E67" s="5"/>
-      <c r="F67" s="5"/>
+      <c r="F67" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
@@ -2143,7 +2225,9 @@
         <v>24</v>
       </c>
       <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
+      <c r="F68" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5"/>
@@ -2213,7 +2297,9 @@
         <v>18</v>
       </c>
       <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
+      <c r="F71" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="5"/>
@@ -2235,7 +2321,9 @@
         <v>24</v>
       </c>
       <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
+      <c r="F72" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
@@ -2257,7 +2345,9 @@
         <v>30</v>
       </c>
       <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
+      <c r="F73" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="5"/>
@@ -2279,7 +2369,9 @@
         <v>36</v>
       </c>
       <c r="E74" s="5"/>
-      <c r="F74" s="5"/>
+      <c r="F74" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="5"/>
@@ -2301,7 +2393,9 @@
         <v>42</v>
       </c>
       <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+      <c r="F75" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="5"/>
@@ -2371,7 +2465,9 @@
         <v>18</v>
       </c>
       <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
+      <c r="F78" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="5"/>
@@ -2393,7 +2489,9 @@
         <v>24</v>
       </c>
       <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="F79" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="5"/>
@@ -2415,7 +2513,9 @@
         <v>30</v>
       </c>
       <c r="E80" s="5"/>
-      <c r="F80" s="5"/>
+      <c r="F80" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="5"/>
@@ -2437,7 +2537,9 @@
         <v>36</v>
       </c>
       <c r="E81" s="5"/>
-      <c r="F81" s="5"/>
+      <c r="F81" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="5"/>
@@ -2459,7 +2561,9 @@
         <v>42</v>
       </c>
       <c r="E82" s="5"/>
-      <c r="F82" s="5"/>
+      <c r="F82" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" s="5"/>
@@ -2529,7 +2633,9 @@
         <v>18</v>
       </c>
       <c r="E85" s="5"/>
-      <c r="F85" s="5"/>
+      <c r="F85" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="5"/>
@@ -2551,7 +2657,9 @@
         <v>24</v>
       </c>
       <c r="E86" s="5"/>
-      <c r="F86" s="5"/>
+      <c r="F86" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="5"/>
@@ -2573,7 +2681,9 @@
         <v>30</v>
       </c>
       <c r="E87" s="5"/>
-      <c r="F87" s="5"/>
+      <c r="F87" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="5"/>
@@ -2595,7 +2705,9 @@
         <v>36</v>
       </c>
       <c r="E88" s="5"/>
-      <c r="F88" s="5"/>
+      <c r="F88" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="5"/>
@@ -2617,7 +2729,9 @@
         <v>42</v>
       </c>
       <c r="E89" s="5"/>
-      <c r="F89" s="5"/>
+      <c r="F89" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="5"/>
@@ -2687,7 +2801,9 @@
         <v>18</v>
       </c>
       <c r="E92" s="5"/>
-      <c r="F92" s="5"/>
+      <c r="F92" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G92" s="5"/>
       <c r="H92" s="5"/>
       <c r="I92" s="5"/>
@@ -2709,7 +2825,9 @@
         <v>24</v>
       </c>
       <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
+      <c r="F93" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
@@ -2717,28 +2835,76 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A94" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B94" s="3">
+        <v>5</v>
+      </c>
       <c r="C94" s="2">
         <v>20000</v>
       </c>
       <c r="D94" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E94" s="5"/>
+      <c r="F94" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+      <c r="I94" s="5"/>
+      <c r="J94" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B95" s="3">
+        <v>6</v>
+      </c>
       <c r="C95" s="2">
         <v>25000</v>
       </c>
       <c r="D95" s="2">
         <v>36</v>
       </c>
-    </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E95" s="5"/>
+      <c r="F95" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+      <c r="I95" s="5"/>
+      <c r="J95" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A96" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96" s="3">
+        <v>7</v>
+      </c>
       <c r="C96" s="2">
         <v>30000</v>
       </c>
       <c r="D96" s="2">
         <v>42</v>
+      </c>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+      <c r="I96" s="5"/>
+      <c r="J96" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/templates/data/revisoes_yamaha.xlsx
+++ b/templates/data/revisoes_yamaha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\yamaha-bot\templates\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2073D8E-1F41-4674-A633-053B46716475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82791B9F-6398-49DB-8FB5-8940A89A28FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CDFE129-51B5-418D-A7F1-200CBCD1D597}"/>
   </bookViews>
@@ -210,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +233,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -595,7 +601,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -614,7 +620,7 @@
       <c r="F2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="9" t="s">
         <v>32</v>
       </c>
       <c r="H2" s="4" t="s">
@@ -627,7 +633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="216" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="247.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -646,7 +652,7 @@
       <c r="F3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="9" t="s">
         <v>28</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -659,7 +665,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="310.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
@@ -672,13 +678,13 @@
       <c r="D4" s="2">
         <v>18</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="10">
         <v>528</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="9" t="s">
         <v>34</v>
       </c>
       <c r="H4" s="7" t="s">
@@ -704,7 +710,9 @@
       <c r="D5" s="2">
         <v>24</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5">
+        <v>330</v>
+      </c>
       <c r="F5" s="5" t="s">
         <v>25</v>
       </c>
@@ -730,7 +738,9 @@
       <c r="D6" s="2">
         <v>30</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="5">
+        <v>636</v>
+      </c>
       <c r="F6" s="5" t="s">
         <v>25</v>
       </c>
@@ -756,7 +766,9 @@
       <c r="D7" s="2">
         <v>36</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5">
+        <v>414</v>
+      </c>
       <c r="F7" s="5" t="s">
         <v>25</v>
       </c>
@@ -782,7 +794,9 @@
       <c r="D8" s="2">
         <v>42</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="5">
+        <v>528</v>
+      </c>
       <c r="F8" s="5" t="s">
         <v>25</v>
       </c>
@@ -808,7 +822,9 @@
       <c r="D9" s="2">
         <v>6</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="5">
+        <v>120</v>
+      </c>
       <c r="F9" s="4" t="s">
         <v>8</v>
       </c>
@@ -832,7 +848,9 @@
       <c r="D10" s="2">
         <v>12</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="5">
+        <v>126</v>
+      </c>
       <c r="F10" s="4" t="s">
         <v>8</v>
       </c>
@@ -856,7 +874,9 @@
       <c r="D11" s="2">
         <v>18</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="5">
+        <v>696</v>
+      </c>
       <c r="F11" s="5" t="s">
         <v>25</v>
       </c>
@@ -880,7 +900,9 @@
       <c r="D12" s="2">
         <v>24</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="5">
+        <v>444</v>
+      </c>
       <c r="F12" s="5" t="s">
         <v>25</v>
       </c>
@@ -904,7 +926,9 @@
       <c r="D13" s="2">
         <v>30</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="5">
+        <v>1098</v>
+      </c>
       <c r="F13" s="5" t="s">
         <v>25</v>
       </c>
@@ -928,7 +952,9 @@
       <c r="D14" s="2">
         <v>36</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5">
+        <v>390</v>
+      </c>
       <c r="F14" s="5" t="s">
         <v>25</v>
       </c>
@@ -952,7 +978,9 @@
       <c r="D15" s="2">
         <v>42</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="5">
+        <v>846</v>
+      </c>
       <c r="F15" s="5" t="s">
         <v>25</v>
       </c>

--- a/templates/data/revisoes_yamaha.xlsx
+++ b/templates/data/revisoes_yamaha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\yamaha-bot\templates\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82791B9F-6398-49DB-8FB5-8940A89A28FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA293C7-1BF3-4921-94C6-FE2CDC19E7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CDFE129-51B5-418D-A7F1-200CBCD1D597}"/>
   </bookViews>

--- a/templates/data/revisoes_yamaha.xlsx
+++ b/templates/data/revisoes_yamaha.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\yamaha-bot\templates\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAA293C7-1BF3-4921-94C6-FE2CDC19E7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{988176C6-D9EC-4A3E-B48A-D492D343397F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7CDFE129-51B5-418D-A7F1-200CBCD1D597}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="45">
   <si>
     <t>modelo</t>
   </si>
@@ -152,6 +152,89 @@
 MANGUEIRA VERIFICAÇÃO DO FILTRO DE AR/ELEMENTO DO FILTRO DE AR DA CAIXA DA CORREIA EM V/FILTRO DE ÓLEO DO MOTOR
 LUBRIFICAÇÃO
 EIXO ARTICULADO DO MANETE DE FREIO DIANTEIRO/EIXO ARTICULADO DO MANETE DE FREIO TRASEIRO/CAVALETE LATERAL/CAVALETE CENTRAL/CABOS E PEÇAS MOVÉIS/MANOPLA DO ACELERADOR</t>
+  </si>
+  <si>
+    <t>LIQUIDO DE ARREFECIMENTO |
+YAMALUBE 10W40 |
+GAXETA DRENO |
+ANEL DE BORRACHA da vareta de óleo |
+CONTRAPINO DA PEDALEIRA</t>
+  </si>
+  <si>
+    <t>VERIFICAÇÃO
+MANGUEIRA DE COMBUSTÍVEL/VELAS DE IGNIÇÃO/INJEÇÃO DE COMBUSTÍVEL/SISTEMA DE ESCAPE/EMBREAGEM/FREIO DIANTEIRO/FREIO TRASEIRO/MANGUEIRAS DO FREIO/RODAS/PNEUS/ROLAMENTOS DA RODA/ROLAMENTOS DA ARTICULAÇÃO DA BALANÇA TRASEIRA/CORRENTE DE TRANSMISSÃO/ROLAMENTO DA DIREÇÃO/FIXAÇÕES DO CHASSI/CAVALETE LATERAL/INTERRUPTOR DO CAVALETE LATERAL/SUSPENSÃO DIANTEIRA/CONJUNTO DO AMORTECEDOR TRASEIRO/BRAÇO RELÊ DA SUSPENSÃO TRASEIRA E PONTOS DE ARTICULAÇÃO DO BRAÇO/ÓLEO DO MOTOR/SISTEMA DE ARREFECIMENTO/INTERRUPTORES DOS FREIOS DIANTEIRO E TRASEIRO/ALOJAMENTO DA MANOPLA DO ACELERADOR E CABO/LUZES, PISCAS E INTERRUPTORES | AJUSTE
+EMBREAGEM/CORRENTE DE TRANSMISSÃO/ALOJAMENTO DA MANOPLA DO ACELERADOR E CABO/LUZES, PISCAS E INTERRUPTORES | LIMPEZA
+VELAS DE IGNIÇÃ/MANGUEIRA DE VERIFICAÇÃO DO FILTRO DE AR | LUBRIFICAÇÃO
+CORRENTE DE TRANSMISSÃO/EIXO ARTICULADO DO MANETE DE FREIO/EIXO ARTICULADO DO PEDAL DE FREIO/EIXO ARTICULADO DO MANETE DA EMBREAGEM/EIXO ARTICULADO DO PEDAL DE CÂMBIO/CAVALETE LATERAL/CABOS E PEÇAS MÓVEIS/ALOJAMENTO DA MANOPLA DO ACELERADOR E CABO</t>
+  </si>
+  <si>
+    <t>YAMALUBE Scooter 10W40 |
+ANEL DE BORRACHA da tampa de abastecimento de óleo do motor |
+CONTRAPINO |
+ANEL TRAVA |
+GAXETA do dreno de óleo do motor |
+VEDAÇÃO DO DUTO DE AR |
+GAXETA DA TAMPA DA CARCACA 1 |</t>
+  </si>
+  <si>
+    <t>YAMALUBE Scooter 10W40 |
+ANEL DE BORRACHA da tampa de abastecimento de óleo do motor |
+CONTRAPINO |
+ANEL TRAVA |
+VELA DE IGNICAO (NGK CR6HSA) |
+GAXETA do dreno de óleo do motor |
+GAXETA do dreno de óleo da transmissão |
+ANEL DE BORRACHA da tampa de abastecimento da transmissão final |
+ANEL DE BORRACHA da tampa do filtro de óleo |
+VEDAÇÃO DO DUTO DE AR |
+GAXETA DA TAMPA DO CABECOTE |
+GAXETA DA TAMPA DA CARCACA 1 |</t>
+  </si>
+  <si>
+    <t>YAMALUBE Scooter 10W40 |
+ANEL DE BORRACHA da tampa de abastecimento de | óleo do motor |
+CONTRAPINO |
+ANEL TRAVA |
+GAXETA do dreno de óleo do motor |
+VEDAÇÃO DO DUTO DE AR |
+GAXETA DA TAMPA DA CARCACA 1 |
+ELEMENTO DO FILTRO DE AR COMP. |</t>
+  </si>
+  <si>
+    <t>YAMALUBE Scooter 10W40 |
+ANEL DE BORRACHA da tampa de abastecimento de óleo do motor |
+CONTRAPINO |
+ANEL TRAVA |
+VELA DE IGNICAO (NGK CR6HSA) |
+GAXETA do dreno de óleo do motor |
+ANEL DE BORRACHA da tampa do filtro de óleo |
+VEDAÇÃO DO DUTO DE AR |
+GAXETA DA TAMPA DO CABECOTE |
+GAXETA DA TAMPA DA CARCACA 1 |</t>
+  </si>
+  <si>
+    <t>YAMALUBE scooter |
+ANEL DE BORRACHA da tampa de enchimento de óleo da transmissão final |
+ANEL DE BORRACHA da tampa de enchimento de óleo |
+ANEL DE BORRACHA tampa peneira de óleo |
+GAXETA DO DRENO |
+GAXETA DO DRENO de óleo da transmissão final |</t>
+  </si>
+  <si>
+    <t>YAMALUBE scooter |
+VEDACAO DO DUTO DE AR |
+ANEL DE BORRACHA da tampa de enchimento de óleo |
+GAXETA DO DRENO |
+VEDACAO DO DUTO DE AR do elemento 1 |
+ANEL DE BORRACHA tampa peneira de óleo |</t>
+  </si>
+  <si>
+    <t>LIQUIDO DE ARREFECIMENTO
+YAMALUBE scooter | ANEL DE BORRACHA da tampa de enchimento de óleo da transmissão final | VEDACAO DO DUTO DE AR | VELA DE IGNICAO |
+GAXETA DO CABECOTE DO CILINDRO | ANEL DE BORRACHA do dreno do radiador | ANEL DE BORRACHA da bomba d' água (maior) |
+ANEL DE BORRACHA da bomba d' água (menor) | ANEL DE BORRACHA do solenóide do comando variável | ANEL DE BORRACHA da tampa de enchimento de óleo |
+GAXETA DO DRENO | GAXETA DO DRENO de óleo da transmissão final | VEDACAO DO DUTO DE AR do elemento 1 | ANEL DE BORRACHA Tampa do radiador |
+GAXETA DA SOLENOIDE VVA | ANEL DE BORRACHA Tampa do radiador 2 | ANEL DE BORRACHA Tampa do radiador 3 | ANEL DE BORRACHA tampa peneira de óleo |</t>
   </si>
 </sst>
 </file>
@@ -697,7 +780,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -716,7 +799,9 @@
       <c r="F5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="7" t="s">
+        <v>38</v>
+      </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5" t="s">
         <v>27</v>
@@ -725,7 +810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -744,7 +829,9 @@
       <c r="F6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5" t="s">
         <v>27</v>
@@ -753,7 +840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>11</v>
       </c>
@@ -772,7 +859,9 @@
       <c r="F7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
         <v>27</v>
@@ -781,7 +870,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -800,7 +889,9 @@
       <c r="F8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="7" t="s">
+        <v>41</v>
+      </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5" t="s">
         <v>27</v>
@@ -809,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -828,14 +919,16 @@
       <c r="F9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="7" t="s">
+        <v>42</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
@@ -854,14 +947,16 @@
       <c r="F10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="250.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
@@ -880,7 +975,9 @@
       <c r="F11" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="5"/>
+      <c r="G11" s="7" t="s">
+        <v>44</v>
+      </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="4" t="s">
@@ -1004,7 +1101,9 @@
       <c r="D16" s="2">
         <v>6</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="5">
+        <v>120</v>
+      </c>
       <c r="F16" s="4" t="s">
         <v>8</v>
       </c>
@@ -1028,7 +1127,9 @@
       <c r="D17" s="2">
         <v>12</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="5">
+        <v>126</v>
+      </c>
       <c r="F17" s="4" t="s">
         <v>8</v>
       </c>
@@ -1052,7 +1153,9 @@
       <c r="D18" s="2">
         <v>18</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="5">
+        <v>696</v>
+      </c>
       <c r="F18" s="5" t="s">
         <v>25</v>
       </c>
@@ -1076,7 +1179,9 @@
       <c r="D19" s="2">
         <v>24</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="5">
+        <v>444</v>
+      </c>
       <c r="F19" s="5" t="s">
         <v>25</v>
       </c>
@@ -1100,7 +1205,9 @@
       <c r="D20" s="2">
         <v>30</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="5">
+        <v>1098</v>
+      </c>
       <c r="F20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1124,7 +1231,9 @@
       <c r="D21" s="2">
         <v>36</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="5">
+        <v>390</v>
+      </c>
       <c r="F21" s="5" t="s">
         <v>25</v>
       </c>
@@ -1148,7 +1257,9 @@
       <c r="D22" s="2">
         <v>42</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="5">
+        <v>846</v>
+      </c>
       <c r="F22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1172,7 +1283,9 @@
       <c r="D23" s="2">
         <v>6</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="5">
+        <v>252</v>
+      </c>
       <c r="F23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1196,7 +1309,9 @@
       <c r="D24" s="2">
         <v>12</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="5">
+        <v>186</v>
+      </c>
       <c r="F24" s="4" t="s">
         <v>8</v>
       </c>
@@ -1220,7 +1335,9 @@
       <c r="D25" s="2">
         <v>18</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="5">
+        <v>426</v>
+      </c>
       <c r="F25" s="5" t="s">
         <v>25</v>
       </c>
@@ -1244,7 +1361,9 @@
       <c r="D26" s="2">
         <v>24</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="5">
+        <v>426</v>
+      </c>
       <c r="F26" s="5" t="s">
         <v>25</v>
       </c>
@@ -1268,7 +1387,9 @@
       <c r="D27" s="2">
         <v>30</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="5">
+        <v>1962</v>
+      </c>
       <c r="F27" s="5" t="s">
         <v>25</v>
       </c>
@@ -1292,7 +1413,9 @@
       <c r="D28" s="2">
         <v>36</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="5">
+        <v>426</v>
+      </c>
       <c r="F28" s="5" t="s">
         <v>25</v>
       </c>
@@ -1316,7 +1439,9 @@
       <c r="D29" s="2">
         <v>42</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="5">
+        <v>426</v>
+      </c>
       <c r="F29" s="5" t="s">
         <v>25</v>
       </c>
@@ -1340,7 +1465,9 @@
       <c r="D30" s="2">
         <v>6</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="5">
+        <v>168</v>
+      </c>
       <c r="F30" s="4" t="s">
         <v>8</v>
       </c>
@@ -1364,7 +1491,9 @@
       <c r="D31" s="2">
         <v>12</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="5">
+        <v>114</v>
+      </c>
       <c r="F31" s="4" t="s">
         <v>8</v>
       </c>
@@ -1388,7 +1517,9 @@
       <c r="D32" s="2">
         <v>18</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="5">
+        <v>414</v>
+      </c>
       <c r="F32" s="5" t="s">
         <v>25</v>
       </c>
@@ -1412,7 +1543,9 @@
       <c r="D33" s="2">
         <v>24</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="5">
+        <v>522</v>
+      </c>
       <c r="F33" s="5" t="s">
         <v>25</v>
       </c>
@@ -1436,7 +1569,9 @@
       <c r="D34" s="2">
         <v>30</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="5">
+        <v>414</v>
+      </c>
       <c r="F34" s="5" t="s">
         <v>25</v>
       </c>
@@ -1460,7 +1595,9 @@
       <c r="D35" s="2">
         <v>36</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="5">
+        <v>252</v>
+      </c>
       <c r="F35" s="5" t="s">
         <v>25</v>
       </c>
@@ -1484,7 +1621,9 @@
       <c r="D36" s="2">
         <v>42</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="5">
+        <v>690</v>
+      </c>
       <c r="F36" s="5" t="s">
         <v>25</v>
       </c>
@@ -1508,7 +1647,9 @@
       <c r="D37" s="2">
         <v>6</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="5">
+        <v>168</v>
+      </c>
       <c r="F37" s="4" t="s">
         <v>8</v>
       </c>
@@ -1532,7 +1673,9 @@
       <c r="D38" s="2">
         <v>12</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="5">
+        <v>150</v>
+      </c>
       <c r="F38" s="4" t="s">
         <v>8</v>
       </c>
@@ -1556,7 +1699,9 @@
       <c r="D39" s="2">
         <v>18</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="5">
+        <v>444</v>
+      </c>
       <c r="F39" s="5" t="s">
         <v>25</v>
       </c>
@@ -1580,7 +1725,9 @@
       <c r="D40" s="2">
         <v>24</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="5">
+        <v>588</v>
+      </c>
       <c r="F40" s="5" t="s">
         <v>25</v>
       </c>
@@ -1604,7 +1751,9 @@
       <c r="D41" s="2">
         <v>30</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="5">
+        <v>444</v>
+      </c>
       <c r="F41" s="5" t="s">
         <v>25</v>
       </c>
@@ -1628,7 +1777,9 @@
       <c r="D42" s="2">
         <v>36</v>
       </c>
-      <c r="E42" s="5"/>
+      <c r="E42" s="5">
+        <v>282</v>
+      </c>
       <c r="F42" s="5" t="s">
         <v>25</v>
       </c>
@@ -1652,7 +1803,9 @@
       <c r="D43" s="2">
         <v>42</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="5">
+        <v>750</v>
+      </c>
       <c r="F43" s="5" t="s">
         <v>25</v>
       </c>
@@ -1676,7 +1829,9 @@
       <c r="D44" s="2">
         <v>6</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="5">
+        <v>324</v>
+      </c>
       <c r="F44" s="4" t="s">
         <v>8</v>
       </c>
@@ -1700,7 +1855,9 @@
       <c r="D45" s="2">
         <v>12</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="5">
+        <v>222</v>
+      </c>
       <c r="F45" s="4" t="s">
         <v>8</v>
       </c>
@@ -1724,7 +1881,9 @@
       <c r="D46" s="2">
         <v>18</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="5">
+        <v>546</v>
+      </c>
       <c r="F46" s="5" t="s">
         <v>25</v>
       </c>
@@ -1748,7 +1907,9 @@
       <c r="D47" s="2">
         <v>24</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="5">
+        <v>360</v>
+      </c>
       <c r="F47" s="5" t="s">
         <v>25</v>
       </c>
@@ -1772,7 +1933,9 @@
       <c r="D48" s="2">
         <v>30</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="5">
+        <v>588</v>
+      </c>
       <c r="F48" s="5" t="s">
         <v>25</v>
       </c>
@@ -1796,7 +1959,9 @@
       <c r="D49" s="2">
         <v>36</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="5">
+        <v>360</v>
+      </c>
       <c r="F49" s="5" t="s">
         <v>25</v>
       </c>
@@ -1820,7 +1985,9 @@
       <c r="D50" s="2">
         <v>42</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="5">
+        <v>546</v>
+      </c>
       <c r="F50" s="5" t="s">
         <v>25</v>
       </c>
@@ -1844,7 +2011,9 @@
       <c r="D51" s="2">
         <v>6</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="5">
+        <v>168</v>
+      </c>
       <c r="F51" s="4" t="s">
         <v>8</v>
       </c>
@@ -1868,7 +2037,9 @@
       <c r="D52" s="2">
         <v>12</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="5">
+        <v>108</v>
+      </c>
       <c r="F52" s="4" t="s">
         <v>8</v>
       </c>
@@ -1892,7 +2063,9 @@
       <c r="D53" s="2">
         <v>18</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="5">
+        <v>426</v>
+      </c>
       <c r="F53" s="5" t="s">
         <v>25</v>
       </c>
@@ -1916,7 +2089,9 @@
       <c r="D54" s="2">
         <v>24</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="5">
+        <v>492</v>
+      </c>
       <c r="F54" s="5" t="s">
         <v>25</v>
       </c>
@@ -1940,7 +2115,9 @@
       <c r="D55" s="2">
         <v>30</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="5">
+        <v>426</v>
+      </c>
       <c r="F55" s="5" t="s">
         <v>25</v>
       </c>
@@ -1964,7 +2141,9 @@
       <c r="D56" s="2">
         <v>36</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="5">
+        <v>246</v>
+      </c>
       <c r="F56" s="5" t="s">
         <v>25</v>
       </c>
@@ -1988,7 +2167,9 @@
       <c r="D57" s="2">
         <v>42</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="5">
+        <v>654</v>
+      </c>
       <c r="F57" s="5" t="s">
         <v>25</v>
       </c>
@@ -2012,7 +2193,9 @@
       <c r="D58" s="2">
         <v>6</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="5">
+        <v>324</v>
+      </c>
       <c r="F58" s="4" t="s">
         <v>8</v>
       </c>
@@ -2036,7 +2219,9 @@
       <c r="D59" s="2">
         <v>12</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="5">
+        <v>222</v>
+      </c>
       <c r="F59" s="4" t="s">
         <v>8</v>
       </c>
@@ -2060,7 +2245,9 @@
       <c r="D60" s="2">
         <v>18</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="5">
+        <v>564</v>
+      </c>
       <c r="F60" s="5" t="s">
         <v>25</v>
       </c>
@@ -2084,7 +2271,9 @@
       <c r="D61" s="2">
         <v>24</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="5">
+        <v>384</v>
+      </c>
       <c r="F61" s="5" t="s">
         <v>25</v>
       </c>
@@ -2108,7 +2297,9 @@
       <c r="D62" s="2">
         <v>30</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="5">
+        <v>612</v>
+      </c>
       <c r="F62" s="5" t="s">
         <v>25</v>
       </c>
@@ -2132,7 +2323,9 @@
       <c r="D63" s="2">
         <v>36</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="5">
+        <v>384</v>
+      </c>
       <c r="F63" s="5" t="s">
         <v>25</v>
       </c>
@@ -2156,7 +2349,9 @@
       <c r="D64" s="2">
         <v>42</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="5">
+        <v>564</v>
+      </c>
       <c r="F64" s="5" t="s">
         <v>25</v>
       </c>
@@ -2444,7 +2639,9 @@
       <c r="D76" s="2">
         <v>6</v>
       </c>
-      <c r="E76" s="5"/>
+      <c r="E76" s="5">
+        <v>402</v>
+      </c>
       <c r="F76" s="4" t="s">
         <v>8</v>
       </c>
@@ -2468,7 +2665,9 @@
       <c r="D77" s="2">
         <v>12</v>
       </c>
-      <c r="E77" s="5"/>
+      <c r="E77" s="5">
+        <v>480</v>
+      </c>
       <c r="F77" s="4" t="s">
         <v>8</v>
       </c>
@@ -2492,7 +2691,9 @@
       <c r="D78" s="2">
         <v>18</v>
       </c>
-      <c r="E78" s="5"/>
+      <c r="E78" s="5">
+        <v>990</v>
+      </c>
       <c r="F78" s="5" t="s">
         <v>25</v>
       </c>
@@ -2516,7 +2717,9 @@
       <c r="D79" s="2">
         <v>24</v>
       </c>
-      <c r="E79" s="5"/>
+      <c r="E79" s="5">
+        <v>960</v>
+      </c>
       <c r="F79" s="5" t="s">
         <v>25</v>
       </c>
@@ -2540,7 +2743,9 @@
       <c r="D80" s="2">
         <v>30</v>
       </c>
-      <c r="E80" s="5"/>
+      <c r="E80" s="5">
+        <v>1350</v>
+      </c>
       <c r="F80" s="5" t="s">
         <v>25</v>
       </c>
@@ -2564,7 +2769,9 @@
       <c r="D81" s="2">
         <v>36</v>
       </c>
-      <c r="E81" s="5"/>
+      <c r="E81" s="5">
+        <v>750</v>
+      </c>
       <c r="F81" s="5" t="s">
         <v>25</v>
       </c>
@@ -2588,7 +2795,9 @@
       <c r="D82" s="2">
         <v>42</v>
       </c>
-      <c r="E82" s="5"/>
+      <c r="E82" s="5">
+        <v>1206</v>
+      </c>
       <c r="F82" s="5" t="s">
         <v>25</v>
       </c>
@@ -2612,7 +2821,9 @@
       <c r="D83" s="2">
         <v>6</v>
       </c>
-      <c r="E83" s="5"/>
+      <c r="E83" s="5">
+        <v>414</v>
+      </c>
       <c r="F83" s="4" t="s">
         <v>8</v>
       </c>
@@ -2636,7 +2847,9 @@
       <c r="D84" s="2">
         <v>12</v>
       </c>
-      <c r="E84" s="5"/>
+      <c r="E84" s="5">
+        <v>552</v>
+      </c>
       <c r="F84" s="4" t="s">
         <v>8</v>
       </c>
@@ -2660,7 +2873,9 @@
       <c r="D85" s="2">
         <v>18</v>
       </c>
-      <c r="E85" s="5"/>
+      <c r="E85" s="5">
+        <v>990</v>
+      </c>
       <c r="F85" s="5" t="s">
         <v>25</v>
       </c>
@@ -2684,7 +2899,9 @@
       <c r="D86" s="2">
         <v>24</v>
       </c>
-      <c r="E86" s="5"/>
+      <c r="E86" s="5">
+        <v>948</v>
+      </c>
       <c r="F86" s="5" t="s">
         <v>25</v>
       </c>
@@ -2708,7 +2925,9 @@
       <c r="D87" s="2">
         <v>30</v>
       </c>
-      <c r="E87" s="5"/>
+      <c r="E87" s="5">
+        <v>1350</v>
+      </c>
       <c r="F87" s="5" t="s">
         <v>25</v>
       </c>
@@ -2732,7 +2951,9 @@
       <c r="D88" s="2">
         <v>36</v>
       </c>
-      <c r="E88" s="5"/>
+      <c r="E88" s="5">
+        <v>750</v>
+      </c>
       <c r="F88" s="5" t="s">
         <v>25</v>
       </c>
@@ -2756,7 +2977,9 @@
       <c r="D89" s="2">
         <v>42</v>
       </c>
-      <c r="E89" s="5"/>
+      <c r="E89" s="5">
+        <v>1188</v>
+      </c>
       <c r="F89" s="5" t="s">
         <v>25</v>
       </c>
@@ -2780,7 +3003,9 @@
       <c r="D90" s="2">
         <v>6</v>
       </c>
-      <c r="E90" s="5"/>
+      <c r="E90" s="5">
+        <v>594</v>
+      </c>
       <c r="F90" s="4" t="s">
         <v>8</v>
       </c>
@@ -2791,7 +3016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>24</v>
       </c>
@@ -2801,19 +3026,13 @@
       <c r="C91" s="2">
         <v>5000</v>
       </c>
-      <c r="D91" s="2">
-        <v>12</v>
-      </c>
+      <c r="D91" s="2"/>
       <c r="E91" s="5"/>
-      <c r="F91" s="4" t="s">
-        <v>8</v>
-      </c>
+      <c r="F91" s="4"/>
       <c r="G91" s="5"/>
       <c r="H91" s="5"/>
       <c r="I91" s="5"/>
-      <c r="J91" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J91" s="4"/>
     </row>
     <row r="92" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
@@ -2826,9 +3045,11 @@
         <v>10000</v>
       </c>
       <c r="D92" s="2">
-        <v>18</v>
-      </c>
-      <c r="E92" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="E92" s="5">
+        <v>342</v>
+      </c>
       <c r="F92" s="5" t="s">
         <v>25</v>
       </c>
@@ -2839,7 +3060,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>24</v>
       </c>
@@ -2849,19 +3070,13 @@
       <c r="C93" s="2">
         <v>15000</v>
       </c>
-      <c r="D93" s="2">
-        <v>24</v>
-      </c>
+      <c r="D93" s="2"/>
       <c r="E93" s="5"/>
-      <c r="F93" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="F93" s="5"/>
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="5"/>
-      <c r="J93" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="J93" s="4"/>
     </row>
     <row r="94" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
@@ -2874,9 +3089,11 @@
         <v>20000</v>
       </c>
       <c r="D94" s="2">
-        <v>30</v>
-      </c>
-      <c r="E94" s="5"/>
+        <v>24</v>
+      </c>
+      <c r="E94" s="5">
+        <v>1152</v>
+      </c>
       <c r="F94" s="5" t="s">
         <v>25</v>
       </c>
@@ -2887,7 +3104,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>24</v>
       </c>
@@ -2897,21 +3114,15 @@
       <c r="C95" s="2">
         <v>25000</v>
       </c>
-      <c r="D95" s="2">
-        <v>36</v>
-      </c>
+      <c r="D95" s="2"/>
       <c r="E95" s="5"/>
-      <c r="F95" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="F95" s="5"/>
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
-      <c r="J95" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="J95" s="4"/>
+    </row>
+    <row r="96" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>24</v>
       </c>
@@ -2922,14 +3133,20 @@
         <v>30000</v>
       </c>
       <c r="D96" s="2">
-        <v>42</v>
-      </c>
-      <c r="E96" s="5"/>
+        <v>36</v>
+      </c>
+      <c r="E96" s="5">
+        <v>708</v>
+      </c>
       <c r="F96" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
+      <c r="G96" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>37</v>
+      </c>
       <c r="I96" s="5"/>
       <c r="J96" s="4" t="s">
         <v>10</v>
